--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f52fe29aaffa8346/Desktop/PatelStoresOrder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87F684E3-E7AD-4D2B-B32D-F3259B7E824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{87F684E3-E7AD-4D2B-B32D-F3259B7E824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{347FC193-571C-447A-9C6D-692181E337A5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8158B175-27BC-4076-B2A3-521A0215E957}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="408">
   <si>
     <t>Product Name</t>
   </si>
@@ -1255,6 +1255,9 @@
   </si>
   <si>
     <t>WIPER</t>
+  </si>
+  <si>
+    <t>01-Umbrella-Black-722651_1.JPG</t>
   </si>
 </sst>
 </file>
@@ -1641,6 +1644,9 @@
       <c r="C2">
         <v>135</v>
       </c>
+      <c r="D2" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f52fe29aaffa8346/Desktop/PatelStoresOrder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{87F684E3-E7AD-4D2B-B32D-F3259B7E824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{347FC193-571C-447A-9C6D-692181E337A5}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{87F684E3-E7AD-4D2B-B32D-F3259B7E824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CDFEAFF-18F5-476E-9174-A9A9F83F0E7C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8158B175-27BC-4076-B2A3-521A0215E957}"/>
   </bookViews>
@@ -1257,7 +1257,7 @@
     <t>WIPER</t>
   </si>
   <si>
-    <t>01-Umbrella-Black-722651_1.JPG</t>
+    <t>images/01-Umbrella-Black-722651_1.JPG</t>
   </si>
 </sst>
 </file>
@@ -1321,6 +1321,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f52fe29aaffa8346/Desktop/PatelStoresOrder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{87F684E3-E7AD-4D2B-B32D-F3259B7E824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CDFEAFF-18F5-476E-9174-A9A9F83F0E7C}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{87F684E3-E7AD-4D2B-B32D-F3259B7E824E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0A99C04-7318-4C03-B6B0-FBE3D3E7A1BC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8158B175-27BC-4076-B2A3-521A0215E957}"/>
   </bookViews>
@@ -1257,7 +1257,7 @@
     <t>WIPER</t>
   </si>
   <si>
-    <t>images/01-Umbrella-Black-722651_1.JPG</t>
+    <t>images/01-Umbrella-Black-722651_1.jpg</t>
   </si>
 </sst>
 </file>
@@ -1324,6 +1324,10 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person0.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
